--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486958_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486958_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.0069</v>
+        <v>6.0655</v>
       </c>
       <c r="E2" t="n">
-        <v>3.598</v>
+        <v>2.6566</v>
       </c>
       <c r="F2" t="n">
         <v>3.4089</v>
@@ -610,10 +610,10 @@
         <v>2.8748</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3051</v>
+        <v>1.3637</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0221</v>
+        <v>1.0807</v>
       </c>
       <c r="U2" t="n">
         <v>0.283</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.577</v>
+        <v>1.1889</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2446</v>
+        <v>1.7677</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6677</v>
+        <v>-0.5788</v>
       </c>
       <c r="G3" t="n">
         <v>-1.2081</v>
@@ -688,13 +688,13 @@
         <v>1.4374</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9829</v>
+        <v>-0.3709</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3216</v>
+        <v>0.2014</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6612</v>
+        <v>-0.5723</v>
       </c>
       <c r="V3" t="n">
         <v>2.3573</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. TRAORE</t>
+          <t>E. MARTINEZ PRETEL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3763</v>
+        <v>1.1048</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.9667</v>
+        <v>-1.2631</v>
       </c>
       <c r="F4" t="n">
-        <v>3.343</v>
+        <v>2.3678</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.4787</v>
+        <v>-3.8974</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.305</v>
+        <v>-1.1551</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.1736</v>
+        <v>-2.7423</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.6294999999999999</v>
+        <v>-2.7669</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0813</v>
+        <v>-0.4638</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.7108</v>
+        <v>-2.3032</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8492</v>
+        <v>-1.1305</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3863</v>
+        <v>-0.6913</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4629</v>
+        <v>-0.4391</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>2.6694</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0534</v>
+        <v>2.6694</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4134</v>
+        <v>0.4251</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4144</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>1.9991</v>
+        <v>0.3401</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5585</v>
+        <v>1.9076</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.6982</v>
+        <v>1.4189</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1396</v>
+        <v>0.4887</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. MARTINEZ PRETEL</t>
+          <t>D. KNOWLES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.301</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.6815</v>
+        <v>0.2951</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9825</v>
+        <v>0.5461</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.8974</v>
+        <v>0.1313</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.1551</v>
+        <v>0.7915</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.7423</v>
+        <v>-0.6602</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.7669</v>
+        <v>0.5122</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.4638</v>
+        <v>0.3149</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.3032</v>
+        <v>0.1973</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1305</v>
+        <v>-0.3809</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6913</v>
+        <v>0.4766</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4391</v>
+        <v>-0.8575</v>
       </c>
       <c r="P5" t="n">
-        <v>2.6694</v>
+        <v>0.616</v>
       </c>
       <c r="Q5" t="n">
+        <v>-1.0267</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.6427</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.5743</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.8096</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.2352</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-0.4805</v>
+      </c>
+      <c r="W5" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="n">
-        <v>2.6694</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-0.3786</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-0.3334</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-0.0452</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.9076</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.4189</v>
-      </c>
       <c r="X5" t="n">
-        <v>0.4887</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. KNOWLES</t>
+          <t>J. SÁNCHEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2153</v>
+        <v>0.5849</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1233</v>
+        <v>1.7813</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3386</v>
+        <v>-1.1964</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1313</v>
+        <v>3.8473</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7915</v>
+        <v>2.0373</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6602</v>
+        <v>1.8101</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5122</v>
+        <v>4.7992</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3149</v>
+        <v>3.0367</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1973</v>
+        <v>1.7626</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3809</v>
+        <v>-0.9519</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4766</v>
+        <v>-0.9994</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8575</v>
+        <v>0.0475</v>
       </c>
       <c r="P6" t="n">
-        <v>0.616</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0267</v>
+        <v>-3.0801</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6427</v>
+        <v>1.8481</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0516</v>
+        <v>-0.402</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3912</v>
+        <v>-0.5271</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4427</v>
+        <v>0.125</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.4805</v>
+        <v>-1.6283</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.4805</v>
+        <v>-2.2176</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. SÁNCHEZ</t>
+          <t>B. TRAORE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1822</v>
+        <v>-0.9611</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4675</v>
+        <v>-3.3851</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2853</v>
+        <v>2.424</v>
       </c>
       <c r="G7" t="n">
-        <v>3.8473</v>
+        <v>-1.4787</v>
       </c>
       <c r="H7" t="n">
-        <v>2.0373</v>
+        <v>-0.305</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8101</v>
+        <v>-1.1736</v>
       </c>
       <c r="J7" t="n">
-        <v>4.7992</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>3.0367</v>
+        <v>0.0813</v>
       </c>
       <c r="L7" t="n">
-        <v>1.7626</v>
+        <v>-0.7108</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9519</v>
+        <v>-0.8492</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9994</v>
+        <v>-0.3863</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0475</v>
+        <v>-0.4629</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.2321</v>
+        <v>-0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.0801</v>
+        <v>-2.0534</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8481</v>
+        <v>2.0534</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8048</v>
+        <v>1.0761</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8409</v>
+        <v>-0.0041</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0361</v>
+        <v>1.0802</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.6283</v>
+        <v>-0.5585</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5893</v>
+        <v>-0.6982</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.2176</v>
+        <v>0.1396</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.3641</v>
+        <v>-2.664</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8598</v>
+        <v>-1.2782</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5043</v>
+        <v>-1.3857</v>
       </c>
       <c r="G8" t="n">
         <v>-3.0514</v>
@@ -1078,13 +1078,13 @@
         <v>0.4107</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0364</v>
+        <v>-0.2635</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2362</v>
+        <v>-0.1822</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1999</v>
+        <v>-0.0813</v>
       </c>
       <c r="V8" t="n">
         <v>0.2402</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3493</v>
+        <v>-3.2133</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7328</v>
+        <v>-2.4189</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6165</v>
+        <v>-0.7943</v>
       </c>
       <c r="G9" t="n">
         <v>-1.6306</v>
@@ -1156,13 +1156,13 @@
         <v>1.0267</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6919</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4611</v>
+        <v>-0.1473</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2308</v>
+        <v>-0.4087</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3633</v>
+        <v>-3.2569</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6945</v>
+        <v>-2.3807</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6688</v>
+        <v>-0.8763</v>
       </c>
       <c r="G10" t="n">
         <v>-2.6236</v>
@@ -1234,13 +1234,13 @@
         <v>2.6694</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4173</v>
+        <v>-0.311</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4729</v>
+        <v>-0.1591</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0556</v>
+        <v>-0.1519</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9384</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.4444</v>
+        <v>-5.5524</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3555</v>
+        <v>-2.8785</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.0889</v>
+        <v>-2.6739</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7916</v>
@@ -1312,13 +1312,13 @@
         <v>1.8481</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2853</v>
+        <v>-0.3933</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2749</v>
+        <v>-0.2481</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5602</v>
+        <v>-0.1452</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1088</v>
@@ -1348,22 +1348,22 @@
         <v>-5.862399999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.104</v>
+        <v>-7.103799999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>1.241500000000001</v>
+        <v>1.2414</v>
       </c>
       <c r="G12" t="n">
         <v>-8.249500000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>0.000100000000000211</v>
+        <v>9.999999999976694e-05</v>
       </c>
       <c r="I12" t="n">
-        <v>-8.2494</v>
+        <v>-8.249400000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>5.1623</v>
+        <v>5.162299999999999</v>
       </c>
       <c r="K12" t="n">
         <v>4.8364</v>
@@ -1381,7 +1381,7 @@
         <v>-8.5753</v>
       </c>
       <c r="P12" t="n">
-        <v>1.0266</v>
+        <v>1.026600000000001</v>
       </c>
       <c r="Q12" t="n">
         <v>-17.4539</v>
@@ -1390,13 +1390,13 @@
         <v>18.4807</v>
       </c>
       <c r="S12" t="n">
-        <v>1.142500000000001</v>
+        <v>1.1426</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9089</v>
+        <v>0.9087999999999998</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2338000000000001</v>
+        <v>0.2337</v>
       </c>
       <c r="V12" t="n">
         <v>0.2176999999999998</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.095599999999999</v>
+        <v>9.702299999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>6.5239</v>
+        <v>6.7332</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5717</v>
+        <v>2.9692</v>
       </c>
       <c r="G13" t="n">
         <v>9.744899999999999</v>
@@ -1468,13 +1468,13 @@
         <v>2.4641</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0682</v>
+        <v>0.5386</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.159</v>
+        <v>0.0502</v>
       </c>
       <c r="U13" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.4883</v>
       </c>
       <c r="V13" t="n">
         <v>0.2402</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.5193</v>
+        <v>5.1112</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2561</v>
+        <v>1.3607</v>
       </c>
       <c r="F14" t="n">
-        <v>4.2631</v>
+        <v>3.7505</v>
       </c>
       <c r="G14" t="n">
         <v>4.5795</v>
@@ -1546,13 +1546,13 @@
         <v>2.6694</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5414</v>
+        <v>1.1333</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0118</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5532</v>
+        <v>1.0405</v>
       </c>
       <c r="V14" t="n">
         <v>-0.8070000000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3944</v>
+        <v>2.8976</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3926</v>
+        <v>-1.7524</v>
       </c>
       <c r="F15" t="n">
-        <v>3.7869</v>
+        <v>4.65</v>
       </c>
       <c r="G15" t="n">
         <v>0.947</v>
@@ -1624,13 +1624,13 @@
         <v>2.8748</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3036</v>
+        <v>0.8068</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7432</v>
+        <v>0.3833</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4396</v>
+        <v>0.4235</v>
       </c>
       <c r="V15" t="n">
         <v>0.9384</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1105</v>
+        <v>2.1733</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4699</v>
+        <v>0.156</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6407</v>
+        <v>2.0173</v>
       </c>
       <c r="G16" t="n">
         <v>1.283</v>
@@ -1702,13 +1702,13 @@
         <v>2.6694</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5688</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5384</v>
+        <v>0.2246</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0304</v>
+        <v>0.407</v>
       </c>
       <c r="V16" t="n">
         <v>-1.1786</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3574</v>
+        <v>1.0496</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6645</v>
+        <v>-1.1415</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0219</v>
+        <v>2.191</v>
       </c>
       <c r="G17" t="n">
         <v>-0.345</v>
@@ -1780,13 +1780,13 @@
         <v>1.6427</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.201</v>
+        <v>0.4911</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3216</v>
+        <v>0.2014</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1206</v>
+        <v>0.2897</v>
       </c>
       <c r="V17" t="n">
         <v>0.6982</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3704</v>
+        <v>-1.0217</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9538</v>
+        <v>-0.7446</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4166</v>
+        <v>-0.2771</v>
       </c>
       <c r="G18" t="n">
         <v>-1.7199</v>
@@ -1858,13 +1858,13 @@
         <v>1.4374</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2398</v>
+        <v>-0.8911</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4534</v>
+        <v>-0.2442</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7864</v>
+        <v>-0.6469</v>
       </c>
       <c r="V18" t="n">
         <v>1.1786</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4003</v>
+        <v>-1.5729</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3432</v>
+        <v>0.2386</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7436</v>
+        <v>-1.8116</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9676</v>
@@ -1936,13 +1936,13 @@
         <v>1.0267</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1833</v>
+        <v>0.0107</v>
       </c>
       <c r="T19" t="n">
-        <v>0.12</v>
+        <v>0.0154</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0633</v>
+        <v>-0.0047</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9469</v>
+        <v>-2.4483</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7097</v>
+        <v>-1.2913</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2371</v>
+        <v>-1.157</v>
       </c>
       <c r="G20" t="n">
         <v>0.2664</v>
@@ -2014,13 +2014,13 @@
         <v>1.2321</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9422</v>
+        <v>-0.4436</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5851</v>
+        <v>-0.1667</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3571</v>
+        <v>-0.2769</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2177</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8054</v>
+        <v>-3.1482</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1856</v>
+        <v>-0.9764</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.6199</v>
+        <v>-2.1718</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3956</v>
@@ -2092,13 +2092,13 @@
         <v>1.0267</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3749</v>
+        <v>-0.7177</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8486</v>
+        <v>-0.6394</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5263</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>-0.8295</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.0917</v>
+        <v>-4.7884</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9284</v>
+        <v>-3.8238</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1633</v>
+        <v>-0.9646</v>
       </c>
       <c r="G22" t="n">
         <v>-4.1432</v>
@@ -2170,13 +2170,13 @@
         <v>0.4107</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9136</v>
+        <v>-0.6102</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2558</v>
+        <v>-0.1512</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6578000000000001</v>
+        <v>-0.4591</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2402</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>5.862499999999998</v>
+        <v>7.954499999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.241499999999999</v>
+        <v>-1.2415</v>
       </c>
       <c r="F23" t="n">
-        <v>7.1038</v>
+        <v>9.195899999999998</v>
       </c>
       <c r="G23" t="n">
         <v>8.249500000000001</v>
@@ -2248,13 +2248,13 @@
         <v>17.454</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1426</v>
+        <v>0.9495000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2336999999999998</v>
+        <v>-0.2338</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9089</v>
+        <v>1.1831</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2175999999999999</v>
